--- a/model_fitting/2010/model3_binary_OR.xlsx
+++ b/model_fitting/2010/model3_binary_OR.xlsx
@@ -700,7 +700,7 @@
         <v>0.666</v>
       </c>
       <c r="D13" t="n">
-        <v>7.744</v>
+        <v>7.743</v>
       </c>
       <c r="E13" t="n">
         <v>0.1903</v>
@@ -740,7 +740,7 @@
         <v>0.13</v>
       </c>
       <c r="D15" t="n">
-        <v>11.003</v>
+        <v>11.002</v>
       </c>
       <c r="E15" t="n">
         <v>0.8743</v>
@@ -780,10 +780,10 @@
         <v>0.491</v>
       </c>
       <c r="D17" t="n">
-        <v>4.891</v>
+        <v>4.89</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4557</v>
+        <v>0.4558</v>
       </c>
       <c r="F17" t="inlineStr"/>
     </row>
@@ -827,7 +827,7 @@
         <v>0.991</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0273</v>
+        <v>0.0274</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
